--- a/Y语言表_Data_Language.xlsx
+++ b/Y语言表_Data_Language.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12345" tabRatio="652"/>
+    <workbookView windowWidth="21000" windowHeight="11475" tabRatio="652" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data_Language" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3328" uniqueCount="2259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3269" uniqueCount="2200">
   <si>
     <t>引导ID</t>
   </si>
@@ -5237,36 +5237,6 @@
     <t>Extra gear refresh spot per round.</t>
   </si>
   <si>
-    <t>UISubscribe_15</t>
-  </si>
-  <si>
-    <t>Daily Sweep &lt;color=#00FF36&gt;+{0}&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>UISubscribe_16</t>
-  </si>
-  <si>
-    <t>Free &lt;color=#00FF36&gt;{0}x&lt;/color&gt; Combat Speed</t>
-  </si>
-  <si>
-    <t>UISubscribe_17</t>
-  </si>
-  <si>
-    <t>Max Stamina &lt;color=#00FF36&gt;+{0}&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>UISubscribe_18</t>
-  </si>
-  <si>
-    <t>Monthly Card</t>
-  </si>
-  <si>
-    <t>UISubscribe_19</t>
-  </si>
-  <si>
-    <t>超值&lt;color=#38FF1DFF&gt;&lt;size=72&gt;{0}%&lt;/size&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
     <t>UILoading_0</t>
   </si>
   <si>
@@ -6590,159 +6560,6 @@
     <t>Получить информацию о сервере</t>
   </si>
   <si>
-    <t>loading_tip1</t>
-  </si>
-  <si>
-    <t>正在前往战场</t>
-  </si>
-  <si>
-    <t>正在前往戰場</t>
-  </si>
-  <si>
-    <t>Heading to the battlefield</t>
-  </si>
-  <si>
-    <t>戦場に向かう</t>
-  </si>
-  <si>
-    <t>전장으로 향합니다</t>
-  </si>
-  <si>
-    <t>Auf dem Weg zum Schlachtfeld</t>
-  </si>
-  <si>
-    <t>Se diriger vers le champ de bataille</t>
-  </si>
-  <si>
-    <t>Dirigiéndose al campo de batalla</t>
-  </si>
-  <si>
-    <t>Andando sul campo di battaglia</t>
-  </si>
-  <si>
-    <t>Indo para o campo de batalha</t>
-  </si>
-  <si>
-    <t>Savaş alanına gidiyor</t>
-  </si>
-  <si>
-    <t>Menuju ke medan perang</t>
-  </si>
-  <si>
-    <t>มุ่งหน้าไปยังสนามรบ</t>
-  </si>
-  <si>
-    <t>Hướng đến chiến trường</t>
-  </si>
-  <si>
-    <t>متجها إلى ساحة المعركة</t>
-  </si>
-  <si>
-    <t>Направляясь на поле битвы</t>
-  </si>
-  <si>
-    <t>loading_tip2</t>
-  </si>
-  <si>
-    <t>检查武器中</t>
-  </si>
-  <si>
-    <t>檢查武器中</t>
-  </si>
-  <si>
-    <t>Check the weapon</t>
-  </si>
-  <si>
-    <t>武器を確認してください</t>
-  </si>
-  <si>
-    <t>무기를 확인하십시오</t>
-  </si>
-  <si>
-    <t>Überprüfen Sie die Waffe</t>
-  </si>
-  <si>
-    <t>Vérifiez l'arme</t>
-  </si>
-  <si>
-    <t>Revisar el arma</t>
-  </si>
-  <si>
-    <t>Controlla l'arma</t>
-  </si>
-  <si>
-    <t>Verifique a arma</t>
-  </si>
-  <si>
-    <t>Silahı kontrol et</t>
-  </si>
-  <si>
-    <t>Periksa senjatanya</t>
-  </si>
-  <si>
-    <t>ตรวจสอบอาวุธ</t>
-  </si>
-  <si>
-    <t>Kiểm tra vũ khí</t>
-  </si>
-  <si>
-    <t>تحقق من السلاح</t>
-  </si>
-  <si>
-    <t>Проверьте оружие</t>
-  </si>
-  <si>
-    <t>loading_tip3</t>
-  </si>
-  <si>
-    <t>等待队友中</t>
-  </si>
-  <si>
-    <t>等待隊友中</t>
-  </si>
-  <si>
-    <t>Wait for teammates to come</t>
-  </si>
-  <si>
-    <t>チームメイトが来るのを待ちます</t>
-  </si>
-  <si>
-    <t>팀원이 올 때까지 기다리십시오</t>
-  </si>
-  <si>
-    <t>Warten Sie, bis Teamkollegen kommen</t>
-  </si>
-  <si>
-    <t>Attendez que les coéquipiers viennent</t>
-  </si>
-  <si>
-    <t>Espera a que vengan los compañeros de equipo</t>
-  </si>
-  <si>
-    <t>Aspetta che arrivi i compagni di squadra</t>
-  </si>
-  <si>
-    <t>Espere que os colegas de equipe venham</t>
-  </si>
-  <si>
-    <t>Takım arkadaşlarının gelmesini bekle</t>
-  </si>
-  <si>
-    <t>Tunggu rekan setimnya datang</t>
-  </si>
-  <si>
-    <t>รอให้เพื่อนร่วมทีมมาถึง</t>
-  </si>
-  <si>
-    <t>Chờ đồng đội đến</t>
-  </si>
-  <si>
-    <t>انتظر حتى يأتي زملاء الفريق</t>
-  </si>
-  <si>
-    <t>Подождите, пока товарищи по команде придут</t>
-  </si>
-  <si>
     <t>loading_tip4</t>
   </si>
   <si>
@@ -6792,6 +6609,12 @@
   </si>
   <si>
     <t>Пополнение силы</t>
+  </si>
+  <si>
+    <t>loading_tip5</t>
+  </si>
+  <si>
+    <t>AAAA</t>
   </si>
 </sst>
 </file>
@@ -6799,10 +6622,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -6868,6 +6691,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
@@ -6876,8 +6707,44 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -6898,23 +6765,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -6928,50 +6781,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6998,8 +6812,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -7026,7 +6849,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7038,7 +6903,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7050,7 +6933,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7068,139 +7023,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7229,17 +7052,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -7249,6 +7068,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -7268,6 +7102,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -7283,46 +7141,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -7334,10 +7157,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="4">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
@@ -7346,133 +7169,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="6">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="4">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -7910,7 +7733,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q321"/>
+  <dimension ref="A1:Q316"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="42.375" style="17" customWidth="1"/>
@@ -16789,121 +16612,6 @@
       <c r="P316" s="19"/>
       <c r="Q316" s="19"/>
     </row>
-    <row r="317" spans="1:17">
-      <c r="A317" s="19" t="s">
-        <v>1740</v>
-      </c>
-      <c r="B317" s="19" t="s">
-        <v>1741</v>
-      </c>
-      <c r="C317" s="19"/>
-      <c r="D317" s="19"/>
-      <c r="E317" s="19"/>
-      <c r="F317" s="19"/>
-      <c r="G317" s="19"/>
-      <c r="H317" s="19"/>
-      <c r="I317" s="19"/>
-      <c r="J317" s="19"/>
-      <c r="K317" s="19"/>
-      <c r="L317" s="19"/>
-      <c r="M317" s="19"/>
-      <c r="N317" s="19"/>
-      <c r="O317" s="19"/>
-      <c r="P317" s="19"/>
-      <c r="Q317" s="19"/>
-    </row>
-    <row r="318" spans="1:17">
-      <c r="A318" s="19" t="s">
-        <v>1742</v>
-      </c>
-      <c r="B318" s="19" t="s">
-        <v>1743</v>
-      </c>
-      <c r="C318" s="19"/>
-      <c r="D318" s="19"/>
-      <c r="E318" s="19"/>
-      <c r="F318" s="19"/>
-      <c r="G318" s="19"/>
-      <c r="H318" s="19"/>
-      <c r="I318" s="19"/>
-      <c r="J318" s="19"/>
-      <c r="K318" s="19"/>
-      <c r="L318" s="19"/>
-      <c r="M318" s="19"/>
-      <c r="N318" s="19"/>
-      <c r="O318" s="19"/>
-      <c r="P318" s="19"/>
-      <c r="Q318" s="19"/>
-    </row>
-    <row r="319" spans="1:17">
-      <c r="A319" s="19" t="s">
-        <v>1744</v>
-      </c>
-      <c r="B319" s="19" t="s">
-        <v>1745</v>
-      </c>
-      <c r="C319" s="19"/>
-      <c r="D319" s="19"/>
-      <c r="E319" s="19"/>
-      <c r="F319" s="19"/>
-      <c r="G319" s="19"/>
-      <c r="H319" s="19"/>
-      <c r="I319" s="19"/>
-      <c r="J319" s="19"/>
-      <c r="K319" s="19"/>
-      <c r="L319" s="19"/>
-      <c r="M319" s="19"/>
-      <c r="N319" s="19"/>
-      <c r="O319" s="19"/>
-      <c r="P319" s="19"/>
-      <c r="Q319" s="19"/>
-    </row>
-    <row r="320" spans="1:17">
-      <c r="A320" s="19" t="s">
-        <v>1746</v>
-      </c>
-      <c r="B320" s="19" t="s">
-        <v>1747</v>
-      </c>
-      <c r="C320" s="19"/>
-      <c r="D320" s="19"/>
-      <c r="E320" s="19"/>
-      <c r="F320" s="19"/>
-      <c r="G320" s="19"/>
-      <c r="H320" s="19"/>
-      <c r="I320" s="19"/>
-      <c r="J320" s="19"/>
-      <c r="K320" s="19"/>
-      <c r="L320" s="19"/>
-      <c r="M320" s="19"/>
-      <c r="N320" s="19"/>
-      <c r="O320" s="19"/>
-      <c r="P320" s="19"/>
-      <c r="Q320" s="19"/>
-    </row>
-    <row r="321" spans="1:17">
-      <c r="A321" s="19" t="s">
-        <v>1748</v>
-      </c>
-      <c r="B321" s="19" t="s">
-        <v>1749</v>
-      </c>
-      <c r="C321" s="19"/>
-      <c r="D321" s="19"/>
-      <c r="E321" s="19"/>
-      <c r="F321" s="19"/>
-      <c r="G321" s="19"/>
-      <c r="H321" s="19"/>
-      <c r="I321" s="19"/>
-      <c r="J321" s="19"/>
-      <c r="K321" s="19"/>
-      <c r="L321" s="19"/>
-      <c r="M321" s="19"/>
-      <c r="N321" s="19"/>
-      <c r="O321" s="19"/>
-      <c r="P321" s="19"/>
-      <c r="Q321" s="19"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="A49">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -16923,7 +16631,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:W37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.2583333333333" style="3" customWidth="1"/>
@@ -17101,749 +16809,749 @@
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:17">
       <c r="A5" s="5" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1743</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>1745</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>1746</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>1748</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>1749</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>1750</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="L5" s="2" t="s">
         <v>1751</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="M5" s="2" t="s">
         <v>1752</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>1753</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>1754</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="P5" s="2" t="s">
         <v>1755</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>1756</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1757</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>1758</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>1759</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>1760</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>1761</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>1762</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>1763</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>1764</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>1765</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>1766</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:17">
       <c r="A6" s="5" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>1762</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>1764</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>1765</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>1767</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="L6" s="2" t="s">
         <v>1768</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="M6" s="2" t="s">
         <v>1769</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>1770</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>1771</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="P6" s="2" t="s">
         <v>1772</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>1773</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>1774</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>1775</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>1776</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>1777</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>1778</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>1779</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>1780</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>1781</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>1782</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:17">
       <c r="A7" s="5" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>1779</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>1780</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>1784</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="L7" s="2" t="s">
         <v>1785</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="M7" s="2" t="s">
         <v>1786</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1787</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>1788</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>1789</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>1790</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>1791</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>1792</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>1793</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>1794</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>1795</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>1796</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>762</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>1797</v>
+        <v>1787</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>1798</v>
+        <v>1788</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>1799</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:17">
       <c r="A8" s="5" t="s">
-        <v>1800</v>
+        <v>1790</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>1801</v>
+        <v>1791</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>1802</v>
+        <v>1792</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>752</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1803</v>
+        <v>1793</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>1804</v>
+        <v>1794</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1805</v>
+        <v>1795</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>756</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1806</v>
+        <v>1796</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1807</v>
+        <v>1797</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>1808</v>
+        <v>1798</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1795</v>
+        <v>1785</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1796</v>
+        <v>1786</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>762</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>1797</v>
+        <v>1787</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>1809</v>
+        <v>1799</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>1810</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:17">
       <c r="A9" s="5" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>1806</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>1807</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>1810</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>1811</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="L9" s="2" t="s">
         <v>1812</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="M9" s="2" t="s">
         <v>1813</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>1815</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="P9" s="2" t="s">
         <v>1816</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>1817</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>1818</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>1819</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>1820</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>1821</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>1822</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>1823</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>1824</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>1825</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>1826</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>1827</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:17">
       <c r="A10" s="5" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>1823</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>1828</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="L10" s="2" t="s">
         <v>1829</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="M10" s="2" t="s">
         <v>1830</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>1831</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>1832</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="P10" s="2" t="s">
         <v>1833</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>1834</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>1835</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>1836</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>1837</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>1838</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>1839</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>1840</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>1841</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>1842</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>1843</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>1844</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:17">
       <c r="A11" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>1840</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>1844</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>1845</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="L11" s="2" t="s">
         <v>1846</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="M11" s="2" t="s">
         <v>1847</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>1848</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="P11" s="2" t="s">
         <v>1850</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="Q11" s="2" t="s">
         <v>1851</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>1852</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>1853</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>1854</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>1855</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>1856</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>1857</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>1858</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>1859</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>1860</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>1861</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:17">
       <c r="A12" s="7" t="s">
-        <v>1862</v>
+        <v>1852</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>1801</v>
+        <v>1791</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1802</v>
+        <v>1792</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>752</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1803</v>
+        <v>1793</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>1804</v>
+        <v>1794</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1805</v>
+        <v>1795</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>756</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>1806</v>
+        <v>1796</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1807</v>
+        <v>1797</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>1808</v>
+        <v>1798</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>1795</v>
+        <v>1785</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1796</v>
+        <v>1786</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>762</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>1797</v>
+        <v>1787</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>1809</v>
+        <v>1799</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>1810</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:17">
       <c r="A13" s="7" t="s">
-        <v>1863</v>
+        <v>1853</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>1762</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>1764</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>1765</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>1768</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="M13" s="2" t="s">
         <v>1769</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="N13" s="2" t="s">
         <v>1770</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>1771</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>1772</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="P13" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="Q13" s="2" t="s">
         <v>1773</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>1774</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>1775</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>1776</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>1777</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>1778</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>1779</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>1780</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>1781</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>1864</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:17">
       <c r="A14" s="7" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>1860</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>1865</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>1866</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>1867</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>1868</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="O14" s="2" t="s">
         <v>1869</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="P14" s="2" t="s">
         <v>1870</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="Q14" s="2" t="s">
         <v>1871</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>1872</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>1873</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>1874</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>1875</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>1876</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>1877</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>1878</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>1879</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>1880</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>1881</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:17">
       <c r="A15" s="7" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>1877</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>1878</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>1879</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>1880</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>1881</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>1882</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="L15" s="2" t="s">
         <v>1883</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="M15" s="2" t="s">
         <v>1884</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>1885</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="O15" s="2" t="s">
         <v>1886</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="P15" s="2" t="s">
         <v>1887</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="Q15" s="2" t="s">
         <v>1888</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>1889</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>1890</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>1891</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>1892</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>1893</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>1894</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>1895</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>1896</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>1897</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>1898</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:17">
       <c r="A16" s="7" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>1892</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>1894</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>1899</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>1900</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>1901</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>1902</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>1903</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="P16" s="2" t="s">
         <v>1904</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>1905</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>1906</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>1907</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>1908</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>1909</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>1910</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>1911</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>1912</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>1913</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>1914</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>1915</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:17">
       <c r="A17" s="7" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1911</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1913</v>
+      </c>
+      <c r="I17" t="s">
+        <v>1914</v>
+      </c>
+      <c r="J17" t="s">
+        <v>1915</v>
+      </c>
+      <c r="K17" t="s">
         <v>1916</v>
       </c>
-      <c r="B17" t="s">
+      <c r="L17" t="s">
         <v>1917</v>
       </c>
-      <c r="C17" t="s">
+      <c r="M17" t="s">
         <v>1918</v>
       </c>
-      <c r="D17" t="s">
+      <c r="N17" t="s">
         <v>1919</v>
       </c>
-      <c r="E17" t="s">
+      <c r="O17" t="s">
         <v>1920</v>
       </c>
-      <c r="F17" t="s">
+      <c r="P17" t="s">
         <v>1921</v>
       </c>
-      <c r="G17" t="s">
+      <c r="Q17" t="s">
         <v>1922</v>
-      </c>
-      <c r="H17" t="s">
-        <v>1923</v>
-      </c>
-      <c r="I17" t="s">
-        <v>1924</v>
-      </c>
-      <c r="J17" t="s">
-        <v>1925</v>
-      </c>
-      <c r="K17" t="s">
-        <v>1926</v>
-      </c>
-      <c r="L17" t="s">
-        <v>1927</v>
-      </c>
-      <c r="M17" t="s">
-        <v>1928</v>
-      </c>
-      <c r="N17" t="s">
-        <v>1929</v>
-      </c>
-      <c r="O17" t="s">
-        <v>1930</v>
-      </c>
-      <c r="P17" t="s">
-        <v>1931</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>1932</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" spans="1:17">
       <c r="A18" s="7" t="s">
-        <v>1933</v>
+        <v>1923</v>
       </c>
       <c r="B18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="C18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="D18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="E18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="F18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="G18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="H18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="I18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="J18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="K18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="L18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="M18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="N18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="O18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="P18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
       <c r="Q18" t="s">
-        <v>1934</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="15" customHeight="1" spans="1:23">
       <c r="A19" s="8" t="s">
-        <v>1935</v>
+        <v>1925</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>251</v>
@@ -17867,31 +17575,31 @@
         <v>256</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>1936</v>
+        <v>1926</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>1937</v>
+        <v>1927</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>1938</v>
+        <v>1928</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>1939</v>
+        <v>1929</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>1940</v>
+        <v>1930</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>1941</v>
+        <v>1931</v>
       </c>
       <c r="O19" s="12" t="s">
-        <v>1942</v>
+        <v>1932</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>1943</v>
+        <v>1933</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>1944</v>
+        <v>1934</v>
       </c>
       <c r="S19" s="8"/>
       <c r="T19" s="12"/>
@@ -17901,7 +17609,7 @@
     </row>
     <row r="20" s="2" customFormat="1" ht="15" customHeight="1" spans="1:23">
       <c r="A20" s="8" t="s">
-        <v>1945</v>
+        <v>1935</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>236</v>
@@ -17925,31 +17633,31 @@
         <v>241</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>1946</v>
+        <v>1936</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>1947</v>
+        <v>1937</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>1948</v>
+        <v>1938</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1949</v>
+        <v>1939</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1950</v>
+        <v>1940</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>1951</v>
+        <v>1941</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>1952</v>
+        <v>1942</v>
       </c>
       <c r="P20" s="13" t="s">
-        <v>1953</v>
+        <v>1943</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>1954</v>
+        <v>1944</v>
       </c>
       <c r="S20" s="8"/>
       <c r="T20" s="12"/>
@@ -17959,55 +17667,55 @@
     </row>
     <row r="21" s="2" customFormat="1" ht="15" customHeight="1" spans="1:23">
       <c r="A21" s="8" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1947</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>1949</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>1950</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>1951</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>1952</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>1953</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>1954</v>
+      </c>
+      <c r="K21" s="12" t="s">
         <v>1955</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="L21" s="2" t="s">
         <v>1956</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="M21" s="2" t="s">
         <v>1957</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>1958</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="O21" s="13" t="s">
         <v>1959</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="P21" s="14" t="s">
         <v>1960</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="Q21" s="12" t="s">
         <v>1961</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>1962</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>1963</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>1964</v>
-      </c>
-      <c r="K21" s="12" t="s">
-        <v>1965</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>1966</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>1967</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>1968</v>
-      </c>
-      <c r="O21" s="13" t="s">
-        <v>1969</v>
-      </c>
-      <c r="P21" s="14" t="s">
-        <v>1970</v>
-      </c>
-      <c r="Q21" s="12" t="s">
-        <v>1971</v>
       </c>
       <c r="S21" s="8"/>
       <c r="T21" s="12"/>
@@ -18017,55 +17725,55 @@
     </row>
     <row r="22" s="2" customFormat="1" ht="15" customHeight="1" spans="1:23">
       <c r="A22" s="8" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>1963</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1965</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>1966</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>1967</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>1968</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>1969</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>1970</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>1971</v>
+      </c>
+      <c r="K22" s="12" t="s">
         <v>1972</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="L22" s="2" t="s">
         <v>1973</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="M22" s="2" t="s">
         <v>1974</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="N22" s="2" t="s">
         <v>1975</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="O22" s="13" t="s">
         <v>1976</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="P22" s="14" t="s">
         <v>1977</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="Q22" s="12" t="s">
         <v>1978</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>1979</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>1980</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>1981</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>1982</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>1983</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>1984</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>1985</v>
-      </c>
-      <c r="O22" s="13" t="s">
-        <v>1986</v>
-      </c>
-      <c r="P22" s="14" t="s">
-        <v>1987</v>
-      </c>
-      <c r="Q22" s="12" t="s">
-        <v>1988</v>
       </c>
       <c r="S22" s="8"/>
       <c r="T22" s="12"/>
@@ -18075,55 +17783,55 @@
     </row>
     <row r="23" s="2" customFormat="1" ht="15" customHeight="1" spans="1:23">
       <c r="A23" s="8" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>1980</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>1983</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>1984</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>1986</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>1987</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>1988</v>
+      </c>
+      <c r="K23" s="12" t="s">
         <v>1989</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="L23" s="2" t="s">
         <v>1990</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="M23" s="2" t="s">
         <v>1991</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="N23" s="2" t="s">
         <v>1992</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="O23" s="12" t="s">
         <v>1993</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="P23" s="14" t="s">
         <v>1994</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="Q23" s="12" t="s">
         <v>1995</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>1996</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>1997</v>
-      </c>
-      <c r="J23" s="12" t="s">
-        <v>1998</v>
-      </c>
-      <c r="K23" s="12" t="s">
-        <v>1999</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>2000</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>2001</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>2002</v>
-      </c>
-      <c r="O23" s="12" t="s">
-        <v>2003</v>
-      </c>
-      <c r="P23" s="14" t="s">
-        <v>2004</v>
-      </c>
-      <c r="Q23" s="12" t="s">
-        <v>2005</v>
       </c>
       <c r="S23" s="8"/>
       <c r="T23" s="12"/>
@@ -18133,7 +17841,7 @@
     </row>
     <row r="24" s="2" customFormat="1" ht="15" customHeight="1" spans="1:23">
       <c r="A24" s="8" t="s">
-        <v>2006</v>
+        <v>1996</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>266</v>
@@ -18142,43 +17850,43 @@
         <v>266</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>2007</v>
+        <v>1997</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>2008</v>
+        <v>1998</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>270</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="P24" s="14" t="s">
-        <v>2018</v>
+        <v>2008</v>
       </c>
       <c r="Q24" s="12" t="s">
         <v>280</v>
@@ -18191,55 +17899,55 @@
     </row>
     <row r="25" s="2" customFormat="1" ht="15" customHeight="1" spans="1:23">
       <c r="A25" s="8" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>2012</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>2013</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>2014</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>2015</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>2016</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>2017</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>2018</v>
+      </c>
+      <c r="K25" s="12" t="s">
         <v>2019</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="L25" s="2" t="s">
         <v>2020</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="M25" s="2" t="s">
         <v>2021</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="N25" s="2" t="s">
         <v>2022</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="O25" s="12" t="s">
         <v>2023</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="P25" s="14" t="s">
         <v>2024</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="Q25" s="12" t="s">
         <v>2025</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>2026</v>
-      </c>
-      <c r="I25" s="12" t="s">
-        <v>2027</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>2028</v>
-      </c>
-      <c r="K25" s="12" t="s">
-        <v>2029</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>2030</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>2031</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>2032</v>
-      </c>
-      <c r="O25" s="12" t="s">
-        <v>2033</v>
-      </c>
-      <c r="P25" s="14" t="s">
-        <v>2034</v>
-      </c>
-      <c r="Q25" s="12" t="s">
-        <v>2035</v>
       </c>
       <c r="S25" s="8"/>
       <c r="T25" s="12"/>
@@ -18249,55 +17957,55 @@
     </row>
     <row r="26" s="2" customFormat="1" ht="15" customHeight="1" spans="1:23">
       <c r="A26" s="11" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>2029</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>2030</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>2031</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>2032</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>2033</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>2034</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>2035</v>
+      </c>
+      <c r="K26" s="12" t="s">
         <v>2036</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="L26" s="2" t="s">
         <v>2037</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="M26" s="2" t="s">
         <v>2038</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="N26" s="2" t="s">
         <v>2039</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="O26" s="12" t="s">
         <v>2040</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="P26" s="14" t="s">
         <v>2041</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="Q26" s="12" t="s">
         <v>2042</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>2043</v>
-      </c>
-      <c r="I26" s="12" t="s">
-        <v>2044</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>2045</v>
-      </c>
-      <c r="K26" s="12" t="s">
-        <v>2046</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>2047</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>2048</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>2049</v>
-      </c>
-      <c r="O26" s="12" t="s">
-        <v>2050</v>
-      </c>
-      <c r="P26" s="14" t="s">
-        <v>2051</v>
-      </c>
-      <c r="Q26" s="12" t="s">
-        <v>2052</v>
       </c>
       <c r="S26" s="8"/>
       <c r="T26" s="12"/>
@@ -18307,55 +18015,55 @@
     </row>
     <row r="27" s="2" customFormat="1" ht="15" customHeight="1" spans="1:23">
       <c r="A27" s="8" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2044</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>2046</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>2047</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>2048</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>2050</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>2051</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>2052</v>
+      </c>
+      <c r="K27" s="12" t="s">
         <v>2053</v>
       </c>
-      <c r="B27" t="s">
+      <c r="L27" s="2" t="s">
         <v>2054</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="M27" s="2" t="s">
         <v>2055</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="N27" s="2" t="s">
         <v>2056</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="O27" s="12" t="s">
         <v>2057</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="P27" s="14" t="s">
         <v>2058</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="Q27" s="12" t="s">
         <v>2059</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>2060</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>2061</v>
-      </c>
-      <c r="J27" s="12" t="s">
-        <v>2062</v>
-      </c>
-      <c r="K27" s="12" t="s">
-        <v>2063</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>2064</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>2065</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>2066</v>
-      </c>
-      <c r="O27" s="12" t="s">
-        <v>2067</v>
-      </c>
-      <c r="P27" s="14" t="s">
-        <v>2068</v>
-      </c>
-      <c r="Q27" s="12" t="s">
-        <v>2069</v>
       </c>
       <c r="S27" s="8"/>
       <c r="T27" s="12"/>
@@ -18365,211 +18073,211 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="8" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2064</v>
+      </c>
+      <c r="F28" t="s">
+        <v>2065</v>
+      </c>
+      <c r="G28" t="s">
+        <v>2066</v>
+      </c>
+      <c r="H28" t="s">
+        <v>2067</v>
+      </c>
+      <c r="I28" t="s">
+        <v>2068</v>
+      </c>
+      <c r="J28" t="s">
+        <v>2069</v>
+      </c>
+      <c r="K28" t="s">
         <v>2070</v>
       </c>
-      <c r="B28" t="s">
+      <c r="L28" t="s">
         <v>2071</v>
       </c>
-      <c r="C28" t="s">
+      <c r="M28" t="s">
         <v>2072</v>
       </c>
-      <c r="D28" t="s">
+      <c r="N28" t="s">
         <v>2073</v>
       </c>
-      <c r="E28" t="s">
+      <c r="O28" t="s">
         <v>2074</v>
       </c>
-      <c r="F28" t="s">
+      <c r="P28" t="s">
         <v>2075</v>
       </c>
-      <c r="G28" t="s">
+      <c r="Q28" t="s">
         <v>2076</v>
-      </c>
-      <c r="H28" t="s">
-        <v>2077</v>
-      </c>
-      <c r="I28" t="s">
-        <v>2078</v>
-      </c>
-      <c r="J28" t="s">
-        <v>2079</v>
-      </c>
-      <c r="K28" t="s">
-        <v>2080</v>
-      </c>
-      <c r="L28" t="s">
-        <v>2081</v>
-      </c>
-      <c r="M28" t="s">
-        <v>2082</v>
-      </c>
-      <c r="N28" t="s">
-        <v>2083</v>
-      </c>
-      <c r="O28" t="s">
-        <v>2084</v>
-      </c>
-      <c r="P28" t="s">
-        <v>2085</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>2086</v>
       </c>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="8" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2080</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F29" t="s">
+        <v>2082</v>
+      </c>
+      <c r="G29" t="s">
+        <v>2083</v>
+      </c>
+      <c r="H29" t="s">
+        <v>2084</v>
+      </c>
+      <c r="I29" t="s">
+        <v>2085</v>
+      </c>
+      <c r="J29" t="s">
+        <v>2086</v>
+      </c>
+      <c r="K29" t="s">
         <v>2087</v>
       </c>
-      <c r="B29" t="s">
+      <c r="L29" t="s">
         <v>2088</v>
       </c>
-      <c r="C29" t="s">
+      <c r="M29" t="s">
         <v>2089</v>
       </c>
-      <c r="D29" t="s">
+      <c r="N29" t="s">
         <v>2090</v>
       </c>
-      <c r="E29" t="s">
+      <c r="O29" t="s">
         <v>2091</v>
       </c>
-      <c r="F29" t="s">
+      <c r="P29" t="s">
         <v>2092</v>
       </c>
-      <c r="G29" t="s">
+      <c r="Q29" t="s">
         <v>2093</v>
-      </c>
-      <c r="H29" t="s">
-        <v>2094</v>
-      </c>
-      <c r="I29" t="s">
-        <v>2095</v>
-      </c>
-      <c r="J29" t="s">
-        <v>2096</v>
-      </c>
-      <c r="K29" t="s">
-        <v>2097</v>
-      </c>
-      <c r="L29" t="s">
-        <v>2098</v>
-      </c>
-      <c r="M29" t="s">
-        <v>2099</v>
-      </c>
-      <c r="N29" t="s">
-        <v>2100</v>
-      </c>
-      <c r="O29" t="s">
-        <v>2101</v>
-      </c>
-      <c r="P29" t="s">
-        <v>2102</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>2103</v>
       </c>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="8" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E30" t="s">
+        <v>2098</v>
+      </c>
+      <c r="F30" t="s">
+        <v>2099</v>
+      </c>
+      <c r="G30" t="s">
+        <v>2100</v>
+      </c>
+      <c r="H30" t="s">
+        <v>2101</v>
+      </c>
+      <c r="I30" t="s">
+        <v>2102</v>
+      </c>
+      <c r="J30" t="s">
+        <v>2103</v>
+      </c>
+      <c r="K30" t="s">
         <v>2104</v>
       </c>
-      <c r="B30" t="s">
+      <c r="L30" t="s">
         <v>2105</v>
       </c>
-      <c r="C30" t="s">
+      <c r="M30" t="s">
         <v>2106</v>
       </c>
-      <c r="D30" t="s">
+      <c r="N30" t="s">
         <v>2107</v>
       </c>
-      <c r="E30" t="s">
+      <c r="O30" t="s">
         <v>2108</v>
       </c>
-      <c r="F30" t="s">
+      <c r="P30" t="s">
         <v>2109</v>
       </c>
-      <c r="G30" t="s">
+      <c r="Q30" t="s">
         <v>2110</v>
-      </c>
-      <c r="H30" t="s">
-        <v>2111</v>
-      </c>
-      <c r="I30" t="s">
-        <v>2112</v>
-      </c>
-      <c r="J30" t="s">
-        <v>2113</v>
-      </c>
-      <c r="K30" t="s">
-        <v>2114</v>
-      </c>
-      <c r="L30" t="s">
-        <v>2115</v>
-      </c>
-      <c r="M30" t="s">
-        <v>2116</v>
-      </c>
-      <c r="N30" t="s">
-        <v>2117</v>
-      </c>
-      <c r="O30" t="s">
-        <v>2118</v>
-      </c>
-      <c r="P30" t="s">
-        <v>2119</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>2120</v>
       </c>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="8" t="s">
-        <v>2121</v>
+        <v>2111</v>
       </c>
       <c r="B31" t="s">
-        <v>2122</v>
+        <v>2112</v>
       </c>
       <c r="C31" t="s">
         <v>266</v>
       </c>
       <c r="D31" t="s">
-        <v>2007</v>
+        <v>1997</v>
       </c>
       <c r="E31" t="s">
-        <v>2008</v>
+        <v>1998</v>
       </c>
       <c r="F31" t="s">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="G31" t="s">
         <v>270</v>
       </c>
       <c r="H31" t="s">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="I31" t="s">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="J31" t="s">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="K31" t="s">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="L31" t="s">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="M31" t="s">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="N31" t="s">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="O31" t="s">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="P31" t="s">
-        <v>2018</v>
+        <v>2008</v>
       </c>
       <c r="Q31" t="s">
         <v>280</v>
@@ -18577,426 +18285,275 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="8" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2114</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E32" t="s">
+        <v>2117</v>
+      </c>
+      <c r="F32" t="s">
+        <v>2118</v>
+      </c>
+      <c r="G32" t="s">
+        <v>2119</v>
+      </c>
+      <c r="H32" t="s">
+        <v>2120</v>
+      </c>
+      <c r="I32" t="s">
+        <v>2121</v>
+      </c>
+      <c r="J32" t="s">
+        <v>2122</v>
+      </c>
+      <c r="K32" t="s">
         <v>2123</v>
       </c>
-      <c r="B32" t="s">
+      <c r="L32" t="s">
         <v>2124</v>
       </c>
-      <c r="C32" t="s">
+      <c r="M32" t="s">
         <v>2125</v>
       </c>
-      <c r="D32" t="s">
+      <c r="N32" t="s">
         <v>2126</v>
       </c>
-      <c r="E32" t="s">
+      <c r="O32" t="s">
         <v>2127</v>
       </c>
-      <c r="F32" t="s">
+      <c r="P32" t="s">
         <v>2128</v>
       </c>
-      <c r="G32" t="s">
+      <c r="Q32" t="s">
         <v>2129</v>
-      </c>
-      <c r="H32" t="s">
-        <v>2130</v>
-      </c>
-      <c r="I32" t="s">
-        <v>2131</v>
-      </c>
-      <c r="J32" t="s">
-        <v>2132</v>
-      </c>
-      <c r="K32" t="s">
-        <v>2133</v>
-      </c>
-      <c r="L32" t="s">
-        <v>2134</v>
-      </c>
-      <c r="M32" t="s">
-        <v>2135</v>
-      </c>
-      <c r="N32" t="s">
-        <v>2136</v>
-      </c>
-      <c r="O32" t="s">
-        <v>2137</v>
-      </c>
-      <c r="P32" t="s">
-        <v>2138</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>2139</v>
       </c>
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="8" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2132</v>
+      </c>
+      <c r="D33" t="s">
+        <v>2133</v>
+      </c>
+      <c r="E33" t="s">
+        <v>2134</v>
+      </c>
+      <c r="F33" t="s">
+        <v>2135</v>
+      </c>
+      <c r="G33" t="s">
+        <v>2136</v>
+      </c>
+      <c r="H33" t="s">
+        <v>2137</v>
+      </c>
+      <c r="I33" t="s">
+        <v>2138</v>
+      </c>
+      <c r="J33" t="s">
+        <v>2139</v>
+      </c>
+      <c r="K33" t="s">
         <v>2140</v>
       </c>
-      <c r="B33" t="s">
+      <c r="L33" t="s">
         <v>2141</v>
       </c>
-      <c r="C33" t="s">
+      <c r="M33" t="s">
         <v>2142</v>
       </c>
-      <c r="D33" t="s">
+      <c r="N33" t="s">
         <v>2143</v>
       </c>
-      <c r="E33" t="s">
+      <c r="O33" t="s">
         <v>2144</v>
       </c>
-      <c r="F33" t="s">
+      <c r="P33" t="s">
         <v>2145</v>
       </c>
-      <c r="G33" t="s">
+      <c r="Q33" t="s">
         <v>2146</v>
-      </c>
-      <c r="H33" t="s">
-        <v>2147</v>
-      </c>
-      <c r="I33" t="s">
-        <v>2148</v>
-      </c>
-      <c r="J33" t="s">
-        <v>2149</v>
-      </c>
-      <c r="K33" t="s">
-        <v>2150</v>
-      </c>
-      <c r="L33" t="s">
-        <v>2151</v>
-      </c>
-      <c r="M33" t="s">
-        <v>2152</v>
-      </c>
-      <c r="N33" t="s">
-        <v>2153</v>
-      </c>
-      <c r="O33" t="s">
-        <v>2154</v>
-      </c>
-      <c r="P33" t="s">
-        <v>2155</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>2156</v>
       </c>
     </row>
     <row r="34" spans="1:17">
       <c r="A34" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2149</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E34" t="s">
+        <v>2151</v>
+      </c>
+      <c r="F34" t="s">
+        <v>2152</v>
+      </c>
+      <c r="G34" t="s">
+        <v>2153</v>
+      </c>
+      <c r="H34" t="s">
+        <v>2154</v>
+      </c>
+      <c r="I34" t="s">
+        <v>2155</v>
+      </c>
+      <c r="J34" t="s">
+        <v>2156</v>
+      </c>
+      <c r="K34" t="s">
         <v>2157</v>
       </c>
-      <c r="B34" t="s">
+      <c r="L34" t="s">
         <v>2158</v>
       </c>
-      <c r="C34" t="s">
+      <c r="M34" t="s">
         <v>2159</v>
       </c>
-      <c r="D34" t="s">
+      <c r="N34" t="s">
         <v>2160</v>
       </c>
-      <c r="E34" t="s">
+      <c r="O34" t="s">
         <v>2161</v>
       </c>
-      <c r="F34" t="s">
+      <c r="P34" t="s">
         <v>2162</v>
       </c>
-      <c r="G34" t="s">
+      <c r="Q34" t="s">
         <v>2163</v>
-      </c>
-      <c r="H34" t="s">
-        <v>2164</v>
-      </c>
-      <c r="I34" t="s">
-        <v>2165</v>
-      </c>
-      <c r="J34" t="s">
-        <v>2166</v>
-      </c>
-      <c r="K34" t="s">
-        <v>2167</v>
-      </c>
-      <c r="L34" t="s">
-        <v>2168</v>
-      </c>
-      <c r="M34" t="s">
-        <v>2169</v>
-      </c>
-      <c r="N34" t="s">
-        <v>2170</v>
-      </c>
-      <c r="O34" t="s">
-        <v>2171</v>
-      </c>
-      <c r="P34" t="s">
-        <v>2172</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>2173</v>
       </c>
     </row>
     <row r="35" spans="1:17">
       <c r="A35" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2167</v>
+      </c>
+      <c r="E35" t="s">
+        <v>2168</v>
+      </c>
+      <c r="F35" t="s">
+        <v>2169</v>
+      </c>
+      <c r="G35" t="s">
+        <v>2170</v>
+      </c>
+      <c r="H35" t="s">
+        <v>2171</v>
+      </c>
+      <c r="I35" t="s">
+        <v>2172</v>
+      </c>
+      <c r="J35" t="s">
+        <v>2173</v>
+      </c>
+      <c r="K35" t="s">
         <v>2174</v>
       </c>
-      <c r="B35" t="s">
+      <c r="L35" t="s">
         <v>2175</v>
       </c>
-      <c r="C35" t="s">
+      <c r="M35" t="s">
         <v>2176</v>
       </c>
-      <c r="D35" t="s">
+      <c r="N35" t="s">
         <v>2177</v>
       </c>
-      <c r="E35" t="s">
+      <c r="O35" t="s">
         <v>2178</v>
       </c>
-      <c r="F35" t="s">
+      <c r="P35" t="s">
         <v>2179</v>
       </c>
-      <c r="G35" t="s">
+      <c r="Q35" t="s">
         <v>2180</v>
-      </c>
-      <c r="H35" t="s">
-        <v>2181</v>
-      </c>
-      <c r="I35" t="s">
-        <v>2182</v>
-      </c>
-      <c r="J35" t="s">
-        <v>2183</v>
-      </c>
-      <c r="K35" t="s">
-        <v>2184</v>
-      </c>
-      <c r="L35" t="s">
-        <v>2185</v>
-      </c>
-      <c r="M35" t="s">
-        <v>2186</v>
-      </c>
-      <c r="N35" t="s">
-        <v>2187</v>
-      </c>
-      <c r="O35" t="s">
-        <v>2188</v>
-      </c>
-      <c r="P35" t="s">
-        <v>2189</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>2190</v>
       </c>
     </row>
     <row r="36" spans="1:17">
       <c r="A36" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2183</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E36" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F36" t="s">
+        <v>2186</v>
+      </c>
+      <c r="G36" t="s">
+        <v>2187</v>
+      </c>
+      <c r="H36" t="s">
+        <v>2188</v>
+      </c>
+      <c r="I36" t="s">
+        <v>2189</v>
+      </c>
+      <c r="J36" t="s">
+        <v>2190</v>
+      </c>
+      <c r="K36" t="s">
         <v>2191</v>
       </c>
-      <c r="B36" t="s">
+      <c r="L36" t="s">
         <v>2192</v>
       </c>
-      <c r="C36" t="s">
+      <c r="M36" t="s">
         <v>2193</v>
       </c>
-      <c r="D36" t="s">
+      <c r="N36" t="s">
         <v>2194</v>
       </c>
-      <c r="E36" t="s">
+      <c r="O36" t="s">
         <v>2195</v>
       </c>
-      <c r="F36" t="s">
+      <c r="P36" t="s">
         <v>2196</v>
       </c>
-      <c r="G36" t="s">
+      <c r="Q36" t="s">
         <v>2197</v>
       </c>
-      <c r="H36" t="s">
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
         <v>2198</v>
       </c>
-      <c r="I36" t="s">
+      <c r="B37" t="s">
         <v>2199</v>
-      </c>
-      <c r="J36" t="s">
-        <v>2200</v>
-      </c>
-      <c r="K36" t="s">
-        <v>2201</v>
-      </c>
-      <c r="L36" t="s">
-        <v>2202</v>
-      </c>
-      <c r="M36" t="s">
-        <v>2203</v>
-      </c>
-      <c r="N36" t="s">
-        <v>2204</v>
-      </c>
-      <c r="O36" t="s">
-        <v>2205</v>
-      </c>
-      <c r="P36" t="s">
-        <v>2206</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>2207</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17">
-      <c r="A37" t="s">
-        <v>2208</v>
-      </c>
-      <c r="B37" t="s">
-        <v>2209</v>
-      </c>
-      <c r="C37" t="s">
-        <v>2210</v>
-      </c>
-      <c r="D37" t="s">
-        <v>2211</v>
-      </c>
-      <c r="E37" t="s">
-        <v>2212</v>
-      </c>
-      <c r="F37" t="s">
-        <v>2213</v>
-      </c>
-      <c r="G37" t="s">
-        <v>2214</v>
-      </c>
-      <c r="H37" t="s">
-        <v>2215</v>
-      </c>
-      <c r="I37" t="s">
-        <v>2216</v>
-      </c>
-      <c r="J37" t="s">
-        <v>2217</v>
-      </c>
-      <c r="K37" t="s">
-        <v>2218</v>
-      </c>
-      <c r="L37" t="s">
-        <v>2219</v>
-      </c>
-      <c r="M37" t="s">
-        <v>2220</v>
-      </c>
-      <c r="N37" t="s">
-        <v>2221</v>
-      </c>
-      <c r="O37" t="s">
-        <v>2222</v>
-      </c>
-      <c r="P37" t="s">
-        <v>2223</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>2224</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17">
-      <c r="A38" t="s">
-        <v>2225</v>
-      </c>
-      <c r="B38" t="s">
-        <v>2226</v>
-      </c>
-      <c r="C38" t="s">
-        <v>2227</v>
-      </c>
-      <c r="D38" t="s">
-        <v>2228</v>
-      </c>
-      <c r="E38" t="s">
-        <v>2229</v>
-      </c>
-      <c r="F38" t="s">
-        <v>2230</v>
-      </c>
-      <c r="G38" t="s">
-        <v>2231</v>
-      </c>
-      <c r="H38" t="s">
-        <v>2232</v>
-      </c>
-      <c r="I38" t="s">
-        <v>2233</v>
-      </c>
-      <c r="J38" t="s">
-        <v>2234</v>
-      </c>
-      <c r="K38" t="s">
-        <v>2235</v>
-      </c>
-      <c r="L38" t="s">
-        <v>2236</v>
-      </c>
-      <c r="M38" t="s">
-        <v>2237</v>
-      </c>
-      <c r="N38" t="s">
-        <v>2238</v>
-      </c>
-      <c r="O38" t="s">
-        <v>2239</v>
-      </c>
-      <c r="P38" t="s">
-        <v>2240</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>2241</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17">
-      <c r="A39" t="s">
-        <v>2242</v>
-      </c>
-      <c r="B39" t="s">
-        <v>2243</v>
-      </c>
-      <c r="C39" t="s">
-        <v>2244</v>
-      </c>
-      <c r="D39" t="s">
-        <v>2245</v>
-      </c>
-      <c r="E39" t="s">
-        <v>2246</v>
-      </c>
-      <c r="F39" t="s">
-        <v>2247</v>
-      </c>
-      <c r="G39" t="s">
-        <v>2248</v>
-      </c>
-      <c r="H39" t="s">
-        <v>2249</v>
-      </c>
-      <c r="I39" t="s">
-        <v>2250</v>
-      </c>
-      <c r="J39" t="s">
-        <v>2251</v>
-      </c>
-      <c r="K39" t="s">
-        <v>2252</v>
-      </c>
-      <c r="L39" t="s">
-        <v>2253</v>
-      </c>
-      <c r="M39" t="s">
-        <v>2254</v>
-      </c>
-      <c r="N39" t="s">
-        <v>2255</v>
-      </c>
-      <c r="O39" t="s">
-        <v>2256</v>
-      </c>
-      <c r="P39" t="s">
-        <v>2257</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>2258</v>
       </c>
     </row>
   </sheetData>
